--- a/data/trans_orig/IP29B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses con lactancia materna exclusiva</t>
+          <t>Meses con lactancia materna exclusiva (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,58</t>
+          <t>6,07; 11,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,9</t>
+          <t>7,06; 13,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,21</t>
+          <t>7,13; 11,29</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 9,67</t>
+          <t>7,56; 9,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 9,57</t>
+          <t>7,66; 9,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 9,23</t>
+          <t>7,87; 9,3</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,18</t>
+          <t>8,36; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,51</t>
+          <t>7,5; 10,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 9,63</t>
+          <t>8,0; 9,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 9,47</t>
+          <t>7,99; 9,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,31</t>
+          <t>8,22; 9,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Estudios-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,93</t>
+          <t>6,06; 11,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 13,0</t>
+          <t>7,38; 13,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,29</t>
+          <t>6,95; 10,98</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 9,56</t>
+          <t>7,61; 9,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 9,47</t>
+          <t>7,6; 9,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 9,3</t>
+          <t>7,85; 9,3</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 11,65</t>
+          <t>8,34; 11,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 10,33</t>
+          <t>7,76; 10,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,29</t>
+          <t>8,19; 10,27</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 9,6</t>
+          <t>7,99; 9,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,5</t>
+          <t>8,02; 9,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 9,32</t>
+          <t>8,17; 9,32</t>
         </is>
       </c>
     </row>
